--- a/enhancements/test-files/12_ARR_pc0101_2026_Oct_reorder_newcol.xlsx
+++ b/enhancements/test-files/12_ARR_pc0101_2026_Oct_reorder_newcol.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -433,223 +433,365 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Transaction Effective Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Policy Effective Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accounting Effective Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Policy Number</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Producer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Insurance Company Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Profit Center Number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Profit Center Name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Commission %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>46043</v>
-      </c>
-      <c r="C2" s="2" t="n">
+      <c r="A2" t="n">
+        <v>674.75</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1148.89</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1823.64</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>46320</v>
       </c>
-      <c r="D2" t="n">
-        <v>10718.12</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15196.96</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>POL-0101-10800</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Metro Agency Group</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Heritage Casualty Co</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>National Indemnity Co</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>101</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Cleveland Office</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8%</t>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="C3" t="n">
+        <v>687.01</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1025.39</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>46296</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>46005</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D3" t="n">
-        <v>13416.88</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>8544.940000000001</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>POL-0101-10801</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Pinnacle Agency Partners</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>National Indemnity Co</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Zenith Insurance Group</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>101</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Cleveland Office</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>11%</t>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
+        <v>636.12</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1415.89</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2052.01</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46022</v>
-      </c>
-      <c r="C4" s="2" t="n">
+      <c r="I4" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>46299</v>
       </c>
-      <c r="D4" t="n">
-        <v>22570.37</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>17100.09</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>POL-0101-10802</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Metro Agency Group</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Liberty Mutual</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Coastal Risk Advisors</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Global Assurance Corp</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>101</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Cleveland Office</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6%</t>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>12%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="C5" t="n">
+        <v>225</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>416.67</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>46298</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>46174</v>
-      </c>
-      <c r="C5" s="2" t="n">
+      <c r="I5" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="J5" s="2" t="n">
         <v>46302</v>
       </c>
-      <c r="D5" t="n">
-        <v>14241.97</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>3472.28</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>POL-0101-10803</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pinnacle Agency Partners</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Brown &amp; Brown</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Global Assurance Corp</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="O5" t="n">
         <v>101</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Cleveland Office</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
